--- a/selection_dates.xlsx
+++ b/selection_dates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2daab8ffa038972/Desktop/Fantasy Cricket/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_F25DC773A252ABDACC104883891D63A25ADE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F799F60D-EE5F-4CD2-AD09-8FC0F821C87A}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="11_F25DC773A252ABDACC104883891D63A25ADE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A18DE499-FA29-4678-9633-296FE8D2FE8E}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="480" windowWidth="17280" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>period_name</t>
   </si>
@@ -40,6 +40,12 @@
   </si>
   <si>
     <t>June2026</t>
+  </si>
+  <si>
+    <t>July2026</t>
+  </si>
+  <si>
+    <t>Aug2026</t>
   </si>
 </sst>
 </file>
@@ -360,7 +366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -399,6 +405,28 @@
         <v>46203</v>
       </c>
     </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46204</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46235</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46265</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/selection_dates.xlsx
+++ b/selection_dates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2daab8ffa038972/Desktop/Fantasy Cricket/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_F25DC773A252ABDACC104883891D63A25ADE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A18DE499-FA29-4678-9633-296FE8D2FE8E}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="11_F25DC773A252ABDACC104883891D63A25ADE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8F4B1DC-53AC-41DB-BCED-2369F16AAFA0}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="480" windowWidth="17280" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
     <t>July2026</t>
   </si>
   <si>
-    <t>Aug2026</t>
+    <t>August2026</t>
   </si>
 </sst>
 </file>
@@ -101,6 +101,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
